--- a/levels_sample.xlsx
+++ b/levels_sample.xlsx
@@ -8,6 +8,7 @@
   <definedNames>
     <definedName name="Parameters">Sheet1!$A$3:$B$6</definedName>
     <definedName name="scoreboard">Sheet1!$D$3:$G$9</definedName>
+    <definedName name="version">Sheet1!$A$11:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -349,7 +350,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -395,7 +396,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.1.2</t>
+          <t>{version}</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -534,6 +535,18 @@
       <c r="G9" s="0" t="inlineStr">
         <is>
           <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>0.1.2</t>
         </is>
       </c>
     </row>
